--- a/graph for C1 and C2.xlsx
+++ b/graph for C1 and C2.xlsx
@@ -1,30 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangyihuan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dream\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93CB79A1-D485-BB4E-8364-0DE03814F677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666EDDAE-1A1D-4436-BE47-B7D6565D76EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3200" yWindow="2200" windowWidth="28100" windowHeight="17360" xr2:uid="{E0C2C5E3-F9FF-8D44-A4DB-FEC9F06EDC85}"/>
+    <workbookView xWindow="3140" yWindow="-10930" windowWidth="19460" windowHeight="10460" xr2:uid="{E0C2C5E3-F9FF-8D44-A4DB-FEC9F06EDC85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$A$16</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$A$17:$A$25</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$16</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$B$17:$B$25</definedName>
-    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$A$16</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$A$17:$A$25</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$B$16</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$B$17:$B$25</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -61,18 +51,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -115,7 +105,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -133,7 +123,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -208,7 +198,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -445,7 +435,7 @@
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
-                  <a:t> Size n(Logarithmic Scale, Base 10)</a:t>
+                  <a:t> Size n (Logarithmic Scale, Base 10)</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-CN" altLang="en-US"/>
               </a:p>
@@ -476,7 +466,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
+              <a:endParaRPr lang="zh-CN" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -569,12 +559,20 @@
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
-                  <a:t> of Key  Conparis	aons(Logarithmic Scale, Base 10)</a:t>
+                  <a:t> of Key  Comparisons (Logarithmic Scale, Base 10)</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-CN" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.4702676382620466E-2"/>
+              <c:y val="0.16859318635505419"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -600,7 +598,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
+              <a:endParaRPr lang="zh-CN" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -728,7 +726,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -773,7 +771,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
-              <a:t>(n= 1,000,000)</a:t>
+              <a:t>(n=1,000,000)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" altLang="zh-CN"/>
           </a:p>
@@ -983,12 +981,20 @@
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
-                  <a:t> S(Logarithmic Scale, Base 2)</a:t>
+                  <a:t> S (Logarithmic Scale, Base 2)</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-CN" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.32134356624953081"/>
+              <c:y val="0.88203045131541224"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1014,7 +1020,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
+              <a:endParaRPr lang="zh-CN" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1136,7 +1142,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
+              <a:endParaRPr lang="zh-CN" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2416,7 +2422,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2733,9 +2739,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFD1321-254A-694C-92CF-5A634633C6E1}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2743,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -2752,7 +2758,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>10000</v>
       </c>
@@ -2760,7 +2766,7 @@
         <v>127054</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>100000</v>
       </c>
@@ -2768,7 +2774,7 @@
         <v>1557587</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1000000</v>
       </c>
@@ -2776,7 +2782,7 @@
         <v>19071486</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>10000000</v>
       </c>
@@ -2784,7 +2790,7 @@
         <v>226426243</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -2792,7 +2798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1</v>
       </c>
@@ -2800,7 +2806,7 @@
         <v>18673888</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2808,7 +2814,7 @@
         <v>18673888</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>4</v>
       </c>
@@ -2816,7 +2822,7 @@
         <v>18728179</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8</v>
       </c>
@@ -2824,7 +2830,7 @@
         <v>19074428</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>16</v>
       </c>
@@ -2832,7 +2838,7 @@
         <v>20225265</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>32</v>
       </c>
@@ -2840,7 +2846,7 @@
         <v>23193587</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>64</v>
       </c>
@@ -2848,7 +2854,7 @@
         <v>29905361</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>128</v>
       </c>
